--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -742,7 +742,7 @@
         <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>28.1</v>
@@ -751,7 +751,7 @@
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -787,10 +787,10 @@
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v>22</v>
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.6</v>
@@ -802,7 +802,7 @@
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.3</v>
+        <v>142.3</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>2.1</v>
@@ -824,13 +824,13 @@
         <v>278.1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>20.8</v>
+        <v>31.4</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>60.8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>10.3</v>
@@ -845,13 +845,13 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.9</v>
+        <v>19.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -860,22 +860,22 @@
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -890,7 +890,7 @@
         <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>21.6</v>
@@ -942,7 +942,7 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.7</v>
@@ -954,7 +954,7 @@
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>27.3</v>
+        <v>22.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.6</v>
@@ -968,14 +968,14 @@
       <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
+      <c r="X6" s="8" t="n">
+        <v>92</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1000,67 +1000,67 @@
         <v>21</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2.1</v>
+        <v>34.5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>96.5</v>
+        <v>6.5</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>11.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>28</v>
+        <v>25.6</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.5</v>
+        <v>54.8</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>73.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1082,70 +1082,70 @@
         <v>33.3</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>21.8</v>
+        <v>2.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>27.5</v>
+        <v>344.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.5</v>
+        <v>54.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20.6</v>
+        <v>60.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.8</v>
+        <v>20.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>22.1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>21.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>25.7</v>
+        <v>28.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>812.1</v>
+        <v>870.6</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>33.3</v>
+        <v>344.6</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>27.9</v>
+        <v>24.4</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>57.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>54.8</v>
+        <v>308</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>23</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>28.1</v>
+        <v>35.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>28.2</v>
+        <v>39.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>74.2</v>
+        <v>389.1</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1167,73 +1167,73 @@
         <v>161.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.4</v>
+        <v>21.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>34.5</v>
+        <v>26.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>54.3</v>
+        <v>10.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.8</v>
+        <v>26.4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>20.9</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>109.4</v>
+        <v>21.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.2</v>
+        <v>21.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.3</v>
+        <v>25.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>3.1</v>
+        <v>927.4</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 066
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>155.6</v>
+        <v>344.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>44.4</v>
+        <v>24.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308 10
-</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>61.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>135.7</v>
+        <v>2.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>272.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>389.1</v>
+        <v>22.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1255,68 +1255,70 @@
         <v>32.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>20.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>31.1</v>
+        <v>33.2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>18</v>
+        <v>563.5</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1332,76 +1334,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>420.3</v>
+        <v>426.3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>331.3</v>
+        <v>23.3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.8</v>
+        <v>23.3</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>933.2</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>56.3</v>
+        <v>58</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>29.5</v>
+        <v>20.8</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1420,73 +1422,73 @@
         <v>418.2</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>32.8</v>
+        <v>3.2</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>12.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.8</v>
+        <v>11.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>23.3</v>
+        <v>21</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>210.4</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.7</v>
+        <v>67.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.8</v>
+        <v>24.3</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>158</v>
+        <v>62.9</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.8</v>
+        <v>13</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>29.6</v>
+        <v>26.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>30.3</v>
+        <v>23.8</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>73.2</v>
+        <v>80.8</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>6.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1502,76 +1504,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>20.8</v>
+        <v>2362.1</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>292.5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>24.9</v>
+        <v>23.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>97</v>
+        <v>998</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>29.1</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>72.3</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1587,76 +1589,80 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>121.4</v>
+        <v>0.6</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>23.5</v>
+        <v>19.3</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+1
+</t>
+        </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>12.1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>60.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>21.1</v>
+        <v>13.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>20.9</v>
+        <v>19.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>9.6</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>27.3</v>
+        <v>6.2</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.8</v>
+        <v>41</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>8.1</v>
+        <v>12.3</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1678,70 +1684,70 @@
         <v>31.4</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>19.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>25.3</v>
+        <v>26.8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>12.1</v>
+        <v>54.5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>2.9</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>22.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>33.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>496</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>30</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>51.4</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>30</v>
+        <v>42.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>71</v>
+        <v>331</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>25</v>
+        <v>76.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>36.5</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>21.9</v>
+        <v>1.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>24.3</v>
+        <v>75.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>386.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.4</v>
+        <v>42.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1757,76 +1763,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5304.1</v>
+        <v>1530.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1524.2</v>
+        <v>54.5</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>99.7</v>
+        <v>199.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>126.8</v>
+        <v>5.4</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>54.5</v>
+        <v>106.9</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>19.7</v>
+        <v>32.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>16.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>28.9</v>
+        <v>206.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.9</v>
+        <v>20.4</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>490</v>
+        <v>98</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>152.4</v>
+        <v>3606.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>85.8</v>
+        <v>25.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.4</v>
+        <v>28.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
+        <v>15.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>136.5</v>
+        <v>22.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.4</v>
+        <v>24.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>386.1</v>
+        <v>725.6</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1842,76 +1848,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
+        <v>606.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>19.9</v>
+        <v>9.4</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.9</v>
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>20.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>39.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>30.5</v>
+        <v>32.2</v>
       </c>
       <c r="R17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="X17" s="3" t="n">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1927,76 +1933,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>336.5</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>32.2</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>19.2</v>
+        <v>26.5</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>25.7</v>
+        <v>46.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>17.2</v>
+        <v>11.7</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>19.4</v>
+        <v>42.1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>20.1</v>
+        <v>18.4</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.1</v>
+        <v>0.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.6</v>
+        <v>88.5</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2012,76 +2018,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
+        <v>299</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>32.2</v>
+        <v>29.7</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>18.8</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4.2</v>
+        <v>42.1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>21.7</v>
+        <v>2.9</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>60.5</v>
+        <v>1.6</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>25.7</v>
+        <v>10.6</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2097,76 +2103,76 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>299</v>
+        <v>35.5</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>14.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>6.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.8</v>
+        <v>18.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>99</v>
+        <v>1006.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>27.9</v>
+        <v>30.1</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.6</v>
+        <v>15.7</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>26.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>51.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2182,37 +2188,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
+        <v>294.9</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>18</v>
+        <v>31.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>24.1</v>
+        <v>29</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.1</v>
+        <v>28.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.9</v>
+        <v>3.5</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61 1
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>22.1</v>
@@ -2221,37 +2230,37 @@
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>26.9</v>
+        <v>22.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>63.1</v>
+        <v>66.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>463.1</v>
+        <v>24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2267,76 +2276,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>294.9</v>
+        <v>1.6</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>18.9</v>
+        <v>55.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>26.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>7.3</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>315.5</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.4</v>
+        <v>88.2</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>10.4</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>18.4</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>19.1</v>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>98.40000000000001</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>19.1</v>
+        <v>97.8</v>
       </c>
       <c r="N22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q22" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>29.9</v>
+        <v>39.7</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>24</v>
+        <v>320</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>22.6</v>
+        <v>78.3</v>
       </c>
       <c r="X22" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2352,76 +2361,79 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
+        <v>322</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>15051.9</v>
+        <v>31.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>96.2</v>
+        <v>12.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>75.8</v>
+        <v>25.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.8</v>
+        <v>11.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>17.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>972.8</v>
+        <v>19.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>122.7</v>
+        <v>22.7</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>98.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
+        <v>30.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1911.6</v>
+        <v>24.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3941.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>320</v>
+        <v>64</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1899.3</v>
+        <v>25.9</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>18.9</v>
+        <v>23.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>405.6</v>
+        <v>28.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>422</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2437,68 +2449,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>31.1</v>
+        <v>30.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>19.2</v>
+        <v>1.8</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11.9</v>
+        <v>10.3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+15156
+</t>
+        </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>24.9</v>
+        <v>0.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X24" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2514,58 +2539,64 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
+        <v>12.8</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>30.1</v>
+        <v>31.7</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1.9</v>
+        <v>19.8</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>44.1</v>
+        <v>26.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>103.5</v>
+        <v>11.2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I25" s="3" t="n"/>
+        <v>18.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J25" s="3" t="n">
-        <v>41.3</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>31.6</v>
+        <v>14.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q25" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>15.2</v>
+        <v>1.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>21</v>
@@ -2574,10 +2605,10 @@
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95.2</v>
+        <v>952.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2595,35 +2626,35 @@
       <c r="C26" s="3" t="n">
         <v>345</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>11.7</v>
+      <c r="D26" s="3" t="n">
+        <v>32.9</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>26.1</v>
+        <v>26.5</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>686.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11.2</v>
+        <v>13.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
@@ -2632,13 +2663,13 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>25.3</v>
@@ -2646,23 +2677,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>20.6</v>
+      <c r="U26" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>27.2</v>
+        <v>22.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.3</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2678,46 +2709,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
+        <v>48.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F27" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.7</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>15.2</v>
+        <v>52.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
+        <v>994</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
@@ -2738,16 +2769,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>25.5</v>
+        <v>65.5</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>74.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2766,46 +2797,46 @@
         <v>282.3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>32.6</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>26.2</v>
+        <v>24.7</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.4</v>
+        <v>190.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>220.1</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2817,7 +2848,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2829,10 +2860,10 @@
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2850,29 +2881,29 @@
       <c r="C29" s="3" t="n">
         <v>140.2</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>29.2</v>
+      <c r="D29" s="8" t="n">
+        <v>58.5</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.3</v>
+        <v>80.3</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>2.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
@@ -2887,7 +2918,7 @@
         <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2899,7 +2930,7 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
@@ -2914,10 +2945,10 @@
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2936,52 +2967,52 @@
         <v>1363.5</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1506.5</v>
+        <v>4.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>99</v>
+        <v>996.1</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>28</v>
+        <v>25.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>56.9</v>
+        <v>1.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>0.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>17.9</v>
+        <v>172.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>23.7</v>
+        <v>5.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>102.2</v>
+        <v>20.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.7</v>
+        <v>172.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>489.5</v>
+        <v>429.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>3545.1</v>
+        <v>3.3</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -2990,19 +3021,23 @@
         <v>68.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>26.7</v>
+        <v>15.3</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+4
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3020,54 +3055,59 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>31.3</v>
+      <c r="D31" s="8" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>25.6</v>
+        <v>16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>20.4</v>
+        <v>61.6</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>71.8</v>
+        <v>26.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>978.9</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>84.2</v>
+      <c r="Q31" s="8" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>22.1</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 89
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="n">
         <v>13.8</v>
@@ -3076,16 +3116,21 @@
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>23.1</v>
+        <v>0.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
+        <v>2.1</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+22
+171971191 7
+</t>
+        </is>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3104,31 +3149,31 @@
         <v>263.5</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>29</v>
+        <v>25.2</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>21.5</v>
@@ -3139,7 +3184,9 @@
       <c r="O32" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P32" s="3" t="n"/>
+      <c r="P32" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
@@ -3147,16 +3194,16 @@
         <v>24.5</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>27.9</v>
+        <v>22.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>638.2</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>27.1</v>
+      <c r="V32" s="8" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>24.5</v>
@@ -3165,10 +3212,15 @@
         <v>25.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717177
+23
+83
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3187,31 +3239,31 @@
         <v>44.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>25.2</v>
+        <v>30.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>22.9</v>
+      <c r="F33" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>29</v>
+        <v>11.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.8</v>
+        <v>2.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
@@ -3220,10 +3272,10 @@
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>98</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
@@ -3232,7 +3284,7 @@
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>83.40000000000001</v>
@@ -3250,10 +3302,10 @@
         <v>21.4</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>948.1</v>
+        <v>28.7</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3269,47 +3321,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>30.6</v>
+        <v>2.4</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>92.5</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>24.9</v>
+      <c r="F34" s="8" t="n">
+        <v>43.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+        <v>10.7</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>20.1</v>
+        <v>19</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>61.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>980.8</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 20
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>25.6</v>
@@ -3318,13 +3375,13 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
+        <v>76.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>26.3</v>
+      <c r="V34" s="8" t="n">
+        <v>63.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>21</v>
@@ -3336,7 +3393,7 @@
         <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3355,7 +3412,7 @@
         <v>284.4</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>29.5</v>
+        <v>28.6</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>18.8</v>
@@ -3364,28 +3421,34 @@
         <v>24.1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1.5</v>
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19</v>
+        <v>0.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3409,7 +3472,7 @@
         <v>9.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>66.3</v>
+        <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
@@ -3421,7 +3484,7 @@
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3439,29 +3502,39 @@
       <c r="C36" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>28.6</v>
+      <c r="D36" s="3" t="n">
+        <v>7.7</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>24.9</v>
+      <c r="F36" s="8" t="n">
+        <v>43.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222725
+1142811042
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.3</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3470,13 +3543,13 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.8</v>
+        <v>20.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3493,20 +3566,20 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>21.4</v>
+      <c r="V36" s="8" t="n">
+        <v>41.4</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>24.2</v>
+        <v>4.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3522,16 +3595,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>826.4</v>
+        <v>22.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>142.9</v>
+        <v>7.7</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>40.1</v>
+        <v>60</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>245.1</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>42.9</v>
@@ -3543,34 +3616,39 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1203444.6</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>44.4</v>
+        <v>1034.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+22
+7
+</t>
+        </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>214.9</v>
+        <v>20.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
+        <v>1334.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>11287.9</v>
+        <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>27.3</v>
+        <v>86.3</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
@@ -3582,16 +3660,14 @@
         <v>124.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="n">
         <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3613,19 +3689,19 @@
         <v>28.6</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>1.8</v>
@@ -3635,7 +3711,7 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.6</v>
+        <v>61.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3644,17 +3720,19 @@
         <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>29.3</v>
+        <v>73.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
@@ -3663,13 +3741,13 @@
         <v>84.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>8324.799999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3688,13 +3766,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
+        <v>32.5</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>30.7</v>
+        <v>36.7</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>25</v>
@@ -3702,58 +3780,64 @@
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>545.5</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>19.5</v>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 29
+15
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.7</v>
+        <v>10.1</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>28.8</v>
+        <v>89.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>15.2</v>
+        <v>666.1</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>42.7</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>28</v>
+        <v>61.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3769,76 +3853,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>242.6</v>
+        <v>28.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>20.8</v>
+        <v>30.8</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>19.4</v>
+        <v>10.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>29.2</v>
+        <v>19.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>98.8</v>
+        <v>990.6</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>29.3</v>
+        <v>36.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>70.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>24.4</v>
+        <v>0.1</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3854,76 +3936,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>288.6</v>
+        <v>242.6</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>30.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>20.4</v>
+        <v>26.8</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>10.5</v>
+        <v>25.2</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>29.2</v>
+        <v>21</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+111
+</t>
+        </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30.9</v>
+        <v>29.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>21.7</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>20.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>29.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>81.8</v>
+        <v>24.4</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3939,74 +4025,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>311.6</v>
+        <v>288.6</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>30.7</v>
+        <v>36.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>21</v>
+        <v>26.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="K42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>10618.2</v>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="3" t="n">
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>84.3</v>
-      </c>
       <c r="Z42" s="3" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4022,10 +4110,10 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>7779.7</v>
+        <v>311.6</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>21</v>
@@ -4034,17 +4122,19 @@
         <v>25.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="K43" s="3" t="n">
-        <v>39.5</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
@@ -4053,31 +4143,41 @@
       <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="R43" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77</v>
+        <v>726</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>95.09999999999999</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>392.3</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>32.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4093,55 +4193,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="8" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>934.6</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>311.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>5465.2</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n">
-        <v>491.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>2461.2</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>46.3</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>726</v>
+      </c>
       <c r="U44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>32.3</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>3242.3</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4156,58 +4280,60 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>290.7</v>
+        <v>1453.4</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>305.1</v>
+        <v>30.5</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>20.4</v>
+        <v>779.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>25.8</v>
+        <v>127.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.1</v>
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>934.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="n">
+        <v>45.9</v>
+      </c>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="n">
+        <v>113.8</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>24.1</v>
+        <v>4.4</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>494.2</v>
+      </c>
+      <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>29.3</v>
+        <v>146.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>64.5</v>
+        <v>24.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>27.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>68.3</v>
+        <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>13.2</v>
+        <v>66.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>26.8</v>
+        <v>71.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>23.8</v>
@@ -4216,10 +4342,10 @@
         <v>27.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>78.5</v>
+        <v>3242.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>7.7</v>
+        <v>38.3</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4234,56 +4360,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="F46" s="3" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>16.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>20.8</v>
+      <c r="K46" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>68.40000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,10 +739,10 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.5</v>
+        <v>335.1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>28.1</v>
@@ -750,62 +750,62 @@
       <c r="G4" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>6.6</v>
+      <c r="H4" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.6</v>
+        <v>21.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>28.1</v>
+      <c r="S4" s="8" t="n">
+        <v>1281.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>142.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -824,13 +824,13 @@
         <v>278.1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>25.2</v>
+        <v>34.1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>25.9</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>10.3</v>
@@ -845,52 +845,52 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>25.4</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
+        <v>12368</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -914,50 +914,48 @@
       <c r="E6" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>10.3</v>
+      <c r="F6" s="8" t="n">
+        <v>206.3</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>410.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>988.5</v>
+        <v>197</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>22.3</v>
+        <v>41.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>59.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>18.6</v>
@@ -965,17 +963,17 @@
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -999,68 +997,68 @@
       <c r="E7" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>26.2</v>
+      <c r="F7" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>20.6</v>
+        <v>11.4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>944.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6.5</v>
+        <v>1980.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>23</v>
+        <v>159.5</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1076,76 +1074,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
+        <v>19368</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>344.5</v>
+      <c r="E8" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>27.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>54.3</v>
+        <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>60.8</v>
+        <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>20.9</v>
+        <v>15.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>22.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>41.7</v>
       </c>
       <c r="N8" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>870.6</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>39.5</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>389.1</v>
+        <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>41.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1161,79 +1159,52 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.6</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>26.4</v>
-      </c>
+        <v>17183.6</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="n">
-        <v>2.4</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>4.2</v>
+        <v>120.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>25.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>927.4</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>4.5</v>
+        <v>1371.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>61.6</v>
+        <v>908</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>190.1</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="n">
-        <v>272.9</v>
+        <v>1032.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>22.8</v>
+        <v>1389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>8.4</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1249,76 +1220,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
+        <v>2356.7</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>18.7</v>
+        <v>10.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>563.5</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>29</v>
+      <c r="X10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>9.4</v>
+        <v>177.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>2.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1334,76 +1303,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>426.3</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>23.3</v>
+        <v>453.1</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>93.3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>26.5</v>
+        <v>89.8</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>18.6</v>
+        <v>13.8</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" s="3" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>28.7</v>
+      <c r="S11" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.6</v>
+        <v>156.3</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>655.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>3.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1419,76 +1388,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>418.2</v>
+        <v>141824</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3.2</v>
+        <v>32.8</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>26.4</v>
+      <c r="V12" s="8" t="n">
+        <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>23.8</v>
+        <v>25.6</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>72.8</v>
+        <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80.8</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1504,76 +1473,74 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2362.1</v>
+        <v>1230.1</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>23.5</v>
+        <v>229.1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>17.8</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>24.6</v>
+      <c r="K13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>998</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>8.4</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="8" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>28.2</v>
+        <v>229.1</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>28.6</v>
-      </c>
       <c r="Y13" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>5</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1589,80 +1556,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.6</v>
+        <v>1821.4</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.4</v>
+        <v>27.6</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.5</v>
+        <v>18.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>9.6</v>
+        <v>198</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.6</v>
+        <v>27.3</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>41</v>
+        <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>12.3</v>
+        <v>18.1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>24.3</v>
+        <v>24</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1680,74 +1643,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>26.8</v>
+        <v>19.3</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>54.5</v>
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.5</v>
+        <v>94.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>7.3</v>
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>33.7</v>
+        <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>51.4</v>
+        <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>42.7</v>
+        <v>25.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>76.3</v>
+        <v>12.3</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>75.8</v>
+        <v>25</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>386.1</v>
+        <v>16.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>42.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1762,77 +1725,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>1530.8</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>54.5</v>
-      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="n">
-        <v>199.2</v>
+        <v>99.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.4</v>
+        <v>126.8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>106.9</v>
+        <v>154.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.4</v>
+        <v>192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>32.9</v>
+        <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>186.4</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>98</v>
+        <v>1490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3606.5</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>152.4</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>66.8</v>
+        <v>1331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>176.3</v>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>725.6</v>
+        <v>1386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>8.5</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1848,76 +1791,72 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>606.4</v>
+        <v>306.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9.4</v>
+        <v>19.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>13</v>
+        <v>25.8</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.5</v>
+        <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>39.4</v>
+        <v>20.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>32.2</v>
+        <v>90.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>58</v>
+        <v>166.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>15.3</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>6.1</v>
+        <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.6</v>
+        <v>1717.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.6</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1933,76 +1872,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>336.5</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46.3</v>
+        <v>32.2</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>18.8</v>
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>67.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>20.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>42.1</v>
+        <v>14</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>28.2</v>
+      <c r="S18" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>25.2</v>
+        <v>158</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>29.2</v>
+        <v>25.1</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>229.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>88.5</v>
+        <v>177.6</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2018,76 +1957,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>299</v>
+        <v>1326.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>19.7</v>
+        <v>92.2</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>26.3</v>
+      <c r="V19" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83</v>
+        <v>188.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2103,76 +2042,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35.5</v>
+        <v>1299</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>24.1</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>6.4</v>
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.8</v>
+        <v>31.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>1006.8</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>24.4</v>
+      <c r="Q20" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>238.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>63.4</v>
+        <v>171.6</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="Y20" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>183</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>35.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2188,79 +2125,74 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>294.9</v>
+        <v>1357.5</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>29</v>
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>24.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>12.4</v>
-      </c>
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61 1
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>19.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>25.8</v>
+        <v>1001</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>66.8</v>
+        <v>163.1</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>88.8</v>
+        <v>184.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2276,76 +2208,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.6</v>
+        <v>1294.9</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>531.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>315.5</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>88.2</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>10.1</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>97.8</v>
+        <v>19.1</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>7.3</v>
+        <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>1.3</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R22" s="8" t="n">
-        <v>24.6</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>39.7</v>
+        <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>320</v>
+        <v>166.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>10.6</v>
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>216.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>442</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>26.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2360,80 +2290,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>11.9</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17.6</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>198.4</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>1252.9</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>64</v>
+        <v>1320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>28.1</v>
-      </c>
+        <v>179.6</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.2</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2449,81 +2350,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1.8</v>
+        <v>322</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>988.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.1</v>
+      <c r="S24" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>164</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.4</v>
+        <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>0.1</v>
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.1</v>
+        <v>184.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.1</v>
+        <v>55.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2539,76 +2431,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12.8</v>
+        <v>177.8</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>31.7</v>
+        <v>30.1</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>26.1</v>
+        <v>4.4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <v>39.8</v>
+      <c r="M25" s="3" t="n">
+        <v>194.4</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>6.9</v>
+        <v>22.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>23.6</v>
+        <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>952.6</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2624,43 +2514,41 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>345</v>
+        <v>2345</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>32.9</v>
+        <v>31.7</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>26.5</v>
+        <v>615.1</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>686.1</v>
+        <v>26.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.1</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
@@ -2668,7 +2556,7 @@
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2677,23 +2565,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
+      <c r="U26" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>26.8</v>
+        <v>62.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>4.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2709,31 +2597,29 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>32.6</v>
+        <v>2418.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>26.8</v>
+        <v>5.4</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>52.4</v>
+        <v>5.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2741,26 +2627,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>994</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2768,17 +2654,17 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
+      <c r="W27" s="8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.2</v>
+        <v>174.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>4.3</v>
+        <v>110.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2796,74 +2682,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>0.2</v>
+      <c r="D28" s="8" t="n">
+        <v>32.6</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>24.7</v>
+        <v>26.8</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>190.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
+        <v>12.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>29.9</v>
+      <c r="M28" s="3" t="n">
+        <v>49.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>23.1</v>
+        <v>33.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>29.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>169.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
+      <c r="X28" s="8" t="n">
+        <v>260.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.8</v>
+        <v>14.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2879,76 +2765,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>58.5</v>
+        <v>120.2</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="F29" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.2</v>
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.2</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>23.7</v>
+        <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3.7</v>
+        <v>173.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W29" s="3" t="n">
+      <c r="V29" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>21.6</v>
+        <v>181.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2963,81 +2849,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>1363.5</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>996.1</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="n">
-        <v>1.4</v>
+        <v>506.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.4</v>
+        <v>192.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>172.1</v>
+        <v>16.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>172.8</v>
-      </c>
+        <v>123.7</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>429.5</v>
+        <v>1489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>344.5</v>
+        <v>1344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
-      </c>
+        <v>168.8</v>
+      </c>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>1411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,82 +2911,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>90.59999999999999</v>
+      <c r="D31" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.3</v>
+        <v>20.1</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>978.9</v>
+        <v>197.9</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>39.1</v>
+        <v>29.1</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 89
-</t>
-        </is>
+        <v>4.2</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>168.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>13.8</v>
+        <v>63.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
-        </is>
+        <v>255.1</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>181.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3146,81 +2992,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.2</v>
+        <v>1263.5</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>19</v>
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="M32" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99</v>
+        <v>990.1</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>22.9</v>
+      <c r="S32" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>69.8</v>
+        <v>169.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>25.8</v>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1717177
-23
-83
-</t>
-        </is>
+        <v>181.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3236,76 +3075,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.1</v>
+        <v>144.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.6</v>
+        <v>25.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>24.9</v>
+      <c r="F33" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.8</v>
+        <v>14.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.1</v>
+        <v>20.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>20.4</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>1.5</v>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>21.4</v>
+      <c r="X33" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.7</v>
+        <v>191.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3321,79 +3156,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>92.5</v>
+        <v>1117.8</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>30.6</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>43.9</v>
+      <c r="F34" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>13.6</v>
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>167.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>61.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>76.2</v>
+        <v>70.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="W34" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>29.3</v>
+        <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.5</v>
+        <v>162.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3409,64 +3239,56 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>28.6</v>
+        <v>1284.4</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>9.5</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+        <v>10.7</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>25.8</v>
+        <v>243.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3478,13 +3300,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>24.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1.3</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3500,41 +3322,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
+        <v>1117.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7.7</v>
+        <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>43.9</v>
+      <c r="F36" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222725
-1142811042
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+        <v>72.5</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3542,14 +3354,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>20.9</v>
+      <c r="N36" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3561,25 +3373,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3595,79 +3407,52 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>826.4</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="n">
-        <v>42.9</v>
+        <v>142.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>17.3</v>
+        <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1034.4</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>103.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>86.3</v>
-      </c>
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
+        <v>140.4</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>1416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.7</v>
+        <v>128</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3683,71 +3468,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
+        <v>163.3</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K38" s="3" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>61.3</v>
+        <v>20</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>73.5</v>
+      <c r="S38" s="8" t="n">
+        <v>927.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8324.799999999999</v>
+        <v>1839.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3766,13 +3549,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>69.3</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>25</v>
@@ -3780,64 +3563,62 @@
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>18</v>
+      <c r="H39" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 29
-15
-</t>
-        </is>
+        <v>93.5</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.6</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>130.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>666.1</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>61.2</v>
+        <v>166.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>2.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.1</v>
+        <v>106.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3853,71 +3634,73 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G40" s="3" t="n">
+      <c r="E40" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="G40" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N40" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>990.6</v>
+        <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>165.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.1</v>
+        <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -3939,77 +3722,73 @@
         <v>242.6</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>26.8</v>
+        <v>29.6</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
+      <c r="I41" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
+        <v>16.9</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98.8</v>
+        <v>193.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
+        <v>720.5</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22.1</v>
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>645.1</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>24.4</v>
+        <v>1841.1</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4028,10 +3807,10 @@
         <v>288.6</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>36.9</v>
+        <v>30.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>26.2</v>
+        <v>20.4</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>25.6</v>
@@ -4039,62 +3818,62 @@
       <c r="G42" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>18.6</v>
+      <c r="H42" s="8" t="n">
+        <v>188.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>1.5</v>
+        <v>16.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>52.8</v>
+        <v>21.2</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10618.2</v>
+        <v>1600</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>0.4</v>
+        <v>162</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>207.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>29.3</v>
+      <c r="X42" s="8" t="n">
+        <v>239.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0.2</v>
+        <v>181.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4110,10 +3889,10 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>30.2</v>
+        <v>2311.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>21</v>
@@ -4124,60 +3903,60 @@
       <c r="G43" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n">
+      <c r="M43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N43" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S43" s="3" t="n">
+      <c r="R43" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>726</v>
+        <v>17</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>2.9</v>
+        <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>84.3</v>
+        <v>184.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4192,80 +3971,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>5465.2</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q44" s="8" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>373.3</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>3242.3</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4280,72 +4009,54 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>779.7</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>127.4</v>
-      </c>
+        <v>1722.7</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="n">
-        <v>50.6</v>
+        <v>6.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>293.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>164.9</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>494.2</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>191.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
+        <v>146.2</v>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>27.6</v>
-      </c>
+        <v>1668</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>3242.3</v>
+        <v>992.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.3</v>
+        <v>198.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4367,70 +4078,68 @@
         <v>30.5</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>20.4</v>
+        <v>803.4</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="8" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>18.7</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>10.5</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.4</v>
+        <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>24.5</v>
+        <v>645.1</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>77.2</v>
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>68.3</v>
+        <v>168.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>32.4</v>
+        <v>292.2</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>26.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,7 +739,7 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>335.1</v>
+        <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>22.7</v>
@@ -750,63 +750,61 @@
       <c r="G4" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
+        <v>22.1</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>27.4</v>
+      <c r="N4" s="8" t="n">
+        <v>76.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="8" t="n">
-        <v>1.7</v>
+      <c r="P4" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>1281.1</v>
+      <c r="S4" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>174.3</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>110</v>
-      </c>
+        <v>1754.3</v>
+      </c>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -824,12 +822,12 @@
         <v>278.1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>34.1</v>
+        <v>31.1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -839,45 +837,45 @@
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.5</v>
+        <v>25.4</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V5" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -887,7 +885,7 @@
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>2.1</v>
@@ -906,74 +904,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12368</v>
+        <v>268.1</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>31.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>206.3</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>410.3</v>
+        <v>63.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>197</v>
+        <v>92</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>41.3</v>
+        <v>27.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -997,23 +997,23 @@
       <c r="E7" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>26.8</v>
+      <c r="F7" s="3" t="n">
+        <v>28.7</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>944.4</v>
+      <c r="H7" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20.3</v>
+        <v>2.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>11.3</v>
+        <v>21.8</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1022,33 +1022,33 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46.1</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>311.9</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>159.5</v>
+        <v>59.5</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>19.1</v>
+        <v>29.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19368</v>
+        <v>9681.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E8" s="8" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
@@ -1095,39 +1095,39 @@
         <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>41.7</v>
+      <c r="M8" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1136,7 +1136,7 @@
       <c r="W8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="8" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1159,49 +1159,73 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>17183.6</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+        <v>1185</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>12100.8</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>120.9</v>
+        <v>20.9</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>128.2</v>
+      </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>124.4</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>1371.5</v>
+        <v>153790.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>908</v>
+        <v>308</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>1420</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>1032.5</v>
+        <v>1139.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1389.1</v>
+        <v>589.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1220,30 +1244,30 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2356.7</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>32.3</v>
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>29.5</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="H10" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="8" t="n">
+        <v>17.5</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>21.9</v>
       </c>
@@ -1254,37 +1278,37 @@
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>197.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>161.6</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>177.8</v>
+        <v>1417.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1303,34 +1327,34 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>453.1</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>93.3</v>
+        <v>35.3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="F11" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>10.4</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1339,10 +1363,10 @@
         <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>33.2</v>
@@ -1350,26 +1374,26 @@
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>156.3</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>655.1</v>
+      <c r="W11" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>12.2</v>
@@ -1388,15 +1412,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>141824</v>
+        <v>1218.2</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>32.8</v>
+        <v>82.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1406,25 +1430,25 @@
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>220.3</v>
+      <c r="N12" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.7</v>
@@ -1439,12 +1463,12 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1958</v>
-      </c>
-      <c r="U12" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1454,10 +1478,10 @@
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>713.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>111.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1473,61 +1497,63 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1230.1</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>229.1</v>
+        <v>230.1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>29.1</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K13" s="8" t="n">
+      <c r="J13" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="R13" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="S13" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1537,10 +1563,10 @@
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>800.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1556,52 +1582,52 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1821.4</v>
+        <v>821.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>80.09999999999999</v>
+      <c r="G14" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>87.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>41.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>24.8</v>
+      <c r="R14" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>28.2</v>
@@ -1610,7 +1636,7 @@
         <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>26</v>
@@ -1618,14 +1644,14 @@
       <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>185.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1643,74 +1669,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>25.3</v>
+        <v>19.5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>12.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="N15" s="8" t="n">
+      <c r="M15" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="8" t="n">
+      <c r="U15" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16.6</v>
+        <v>716.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1725,57 +1751,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>15308.1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1524.2</v>
+      </c>
       <c r="E16" s="3" t="n">
-        <v>99.7</v>
+        <v>99.2</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>126.8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>154.5</v>
+        <v>524.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>192.1</v>
+        <v>19.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>162.4</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1129</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>1490</v>
+        <v>490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>142.7</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>1331</v>
+        <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>140</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1386.1</v>
+        <v>13861.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>42.3</v>
+        <v>14.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1800,63 +1846,67 @@
         <v>19.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G17" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>23.8</v>
+      <c r="N17" s="8" t="n">
+        <v>888.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>90.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>166.2</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="V17" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="n">
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1717.2</v>
+        <v>141.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1872,76 +1922,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>3341.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>32.2</v>
+        <v>36.4</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>67.2</v>
+        <v>171.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>20.4</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>19.7</v>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>69.7</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V18" s="8" t="n">
+      <c r="U18" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>229.8</v>
+        <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>177.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1957,12 +2007,12 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1326.2</v>
+        <v>326.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="E19" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="F19" s="3" t="n">
@@ -1971,29 +2021,29 @@
       <c r="G19" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>24.3</v>
+      <c r="N19" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.4</v>
@@ -2002,15 +2052,15 @@
         <v>31.7</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S19" s="8" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="S19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="U19" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U19" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="V19" s="8" t="n">
@@ -2019,11 +2069,11 @@
       <c r="W19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.8</v>
@@ -2042,13 +2092,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1299</v>
+        <v>2899</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>89.7</v>
+        <v>29.7</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>24.7</v>
@@ -2057,41 +2107,43 @@
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>31.5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>22.8</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>238.4</v>
+      <c r="R20" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>171.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.6</v>
@@ -2102,11 +2154,11 @@
       <c r="W20" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>5.4</v>
@@ -2125,56 +2177,58 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1357.5</v>
+        <v>357.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="G21" s="8" t="n">
+        <v>828.1</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>16.4</v>
+      </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
+        <v>12.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>12.8</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>163.1</v>
+        <v>63.1</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>15.7</v>
@@ -2182,17 +2236,17 @@
       <c r="V21" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>184.1</v>
+        <v>18484.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2208,32 +2262,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1294.9</v>
+        <v>992.9</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>531.2</v>
+        <v>21.2</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17.4</v>
+        <v>11.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="K22" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2242,12 +2298,12 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>31</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2257,19 +2313,19 @@
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>216.5</v>
+      <c r="X22" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>88.8</v>
@@ -2290,15 +2346,23 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1610.1</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>125.8</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2306,35 +2370,53 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>16.5</v>
+      </c>
       <c r="L23" s="3" t="n">
-        <v>198.4</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1613.3</v>
+      </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>152.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>115394.7</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>1320</v>
+        <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>796.1</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>140.6</v>
+      </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>126.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2350,13 +2432,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
+        <v>32</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>25.2</v>
@@ -2368,36 +2450,38 @@
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>1.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="8" t="n">
-        <v>29.7</v>
+      <c r="L24" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>22.7</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>988.1</v>
+        <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="R24" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2405,17 +2489,17 @@
       <c r="V24" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>55.3</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2515,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
+        <v>171.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>30.1</v>
@@ -2440,35 +2524,37 @@
         <v>19.8</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.4</v>
+        <v>24.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>17.6</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
@@ -2476,29 +2562,29 @@
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>95.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2514,29 +2600,31 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>31.7</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>615.1</v>
-      </c>
-      <c r="F26" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>886.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2548,19 +2636,19 @@
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>55.2</v>
@@ -2568,17 +2656,17 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>62.1</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>174.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2597,29 +2685,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2418.2</v>
+        <v>1418.2</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H27" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="n">
+        <v>13.1</v>
+      </c>
       <c r="J27" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2627,26 +2717,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2655,16 +2745,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>174.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>110.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2695,61 +2785,61 @@
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>12.6</v>
+        <v>80</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>49.9</v>
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>33.4</v>
+        <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>29.7</v>
+        <v>979.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>224.4</v>
-      </c>
-      <c r="W28" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>260.3</v>
+        <v>659.5</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>0.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2855,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>120.2</v>
+        <v>122112.1</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.2</v>
@@ -2774,7 +2864,7 @@
         <v>20.3</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>24.7</v>
+        <v>47.2</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.9</v>
@@ -2783,30 +2873,28 @@
         <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
+      <c r="M29" s="3" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="N29" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
@@ -2816,25 +2904,25 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.8</v>
+        <v>181.9</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2849,48 +2937,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>625.1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1120</v>
+      </c>
       <c r="G30" s="3" t="n">
-        <v>506.9</v>
+        <v>569.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>192.2</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.7</v>
+        <v>114.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>123.7</v>
       </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>122.8</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>1489.5</v>
+        <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>1344.5</v>
+        <v>344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>68.8</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>13.3</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>1411.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -2911,72 +3025,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>31.3</v>
+      <c r="D31" s="8" t="n">
+        <v>1246.1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>11.9</v>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>197.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>255.1</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>23.1</v>
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>206.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>181.3</v>
+        <v>182.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>1682.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2992,15 +3106,15 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1263.5</v>
-      </c>
-      <c r="D32" s="8" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3010,23 +3124,25 @@
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>990.1</v>
+        <v>99</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3034,32 +3150,32 @@
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>169.8</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>29.1</v>
+      <c r="X32" s="3" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3191,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>144.1</v>
+        <v>44.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>25.2</v>
@@ -3087,17 +3203,19 @@
         <v>22.9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>129</v>
+        <v>4.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
+      <c r="J33" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3105,42 +3223,44 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3156,12 +3276,12 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1117.8</v>
+        <v>117.2</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="F34" s="3" t="n">
@@ -3171,7 +3291,7 @@
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>167.8</v>
+        <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
@@ -3190,40 +3310,40 @@
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>162.5</v>
+        <v>62.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>182.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3239,15 +3359,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1284.4</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3257,23 +3377,25 @@
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="n">
-        <v>243.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>10</v>
@@ -3281,14 +3403,14 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>275.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3299,14 +3421,14 @@
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>29.3</v>
+      <c r="X35" s="8" t="n">
+        <v>2959.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>164.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3334,10 +3456,10 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>72.5</v>
+        <v>7.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3346,7 +3468,7 @@
         <v>11</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>16.3</v>
+        <v>11.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3354,14 +3476,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3373,25 +3495,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>15.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3409,47 +3531,71 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1121.5</v>
+      </c>
       <c r="G37" s="3" t="n">
-        <v>142.9</v>
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="K37" s="3" t="n">
         <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="P37" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>233.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>136.3</v>
+      </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+        <v>40.4</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>129.8</v>
+      </c>
       <c r="Y37" s="3" t="n">
-        <v>1416</v>
+        <v>12466</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128</v>
@@ -3468,13 +3614,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>163.3</v>
+        <v>155.3</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>24.3</v>
@@ -3482,55 +3628,59 @@
       <c r="G38" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>68.59999999999999</v>
+      <c r="H38" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>927.3</v>
+      <c r="S38" s="3" t="n">
+        <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
+        <v>828.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1839.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3549,13 +3699,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>69.3</v>
+        <v>332</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>25</v>
@@ -3564,16 +3714,16 @@
         <v>11.4</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>93.5</v>
+        <v>9.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.5</v>
@@ -3585,13 +3735,13 @@
         <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>130.7</v>
+        <v>0.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
@@ -3600,25 +3750,25 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>166.5</v>
+        <v>6685.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>27.2</v>
+        <v>17.8</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>106.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3634,7 +3784,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.1</v>
+        <v>278.8</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>30.8</v>
@@ -3642,68 +3792,68 @@
       <c r="E40" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>229.7</v>
-      </c>
-      <c r="G40" s="8" t="n">
+      <c r="F40" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G40" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+      <c r="H40" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>25.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V40" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>1811.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3719,77 +3869,75 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>242.6</v>
+        <v>248.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>18.5</v>
+      <c r="I41" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>193.8</v>
+        <v>93.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
-      </c>
-      <c r="U41" s="8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="8" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>645.1</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>1841.1</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>16.7</v>
-      </c>
+        <v>181.1</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3819,55 +3967,55 @@
         <v>10.5</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>0.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>91.2</v>
+      <c r="M42" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q42" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>207.1</v>
+      <c r="V42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>239.3</v>
+        <v>8953.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>181.8</v>
@@ -3889,12 +4037,12 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2311.6</v>
+        <v>312.6</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="8" t="n">
         <v>21</v>
       </c>
       <c r="F43" s="3" t="n">
@@ -3906,7 +4054,9 @@
       <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>41.6</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
       </c>
@@ -3916,47 +4066,47 @@
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N43" s="8" t="n">
+      <c r="M43" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>35.4</v>
+        <v>95.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>184.3</v>
+        <v>1849.5</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3971,7 +4121,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
@@ -4009,54 +4161,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1722.7</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
+        <v>1423.4</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>922.7</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>10101.1</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>6.1</v>
+        <v>12101</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>293.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>164.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>100900160.4</v>
+      </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>16128.5</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>191.8</v>
+        <v>4916</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1246.3</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1668</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>1412.4</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>122.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>992.3</v>
+        <v>3983.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>198.5</v>
+        <v>10820.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4074,72 +4246,74 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="8" t="n">
         <v>30.5</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>803.4</v>
+        <v>20.4</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>18.7</v>
+        <v>11.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>20.6</v>
+      <c r="M46" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>198.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>29.3</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>645.1</v>
+        <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>27.7</v>
+        <v>71.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>22.6</v>
+        <v>73.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>18.5</v>
+        <v>128.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>7.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,7 +739,7 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>22.7</v>
@@ -757,7 +757,7 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>22.1</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -768,14 +768,14 @@
       <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>76.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.7</v>
+        <v>6.1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
@@ -783,7 +783,7 @@
       <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -798,11 +798,11 @@
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>29.1</v>
+      <c r="X4" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1754.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -837,10 +837,10 @@
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>31.1</v>
+        <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
@@ -848,8 +848,8 @@
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>21.4</v>
+      <c r="M5" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -870,7 +870,7 @@
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>8.4</v>
@@ -881,7 +881,7 @@
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>268.1</v>
+        <v>368</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>63.5</v>
+      <c r="F6" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>10.3</v>
+        <v>20.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -925,7 +925,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -940,13 +940,13 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>972</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
-        <v>12.4</v>
+      <c r="Q6" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>24.9</v>
@@ -958,7 +958,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
@@ -970,10 +970,10 @@
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>45.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
+        <v>8218.200000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>32.4</v>
@@ -998,22 +998,22 @@
         <v>21</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1042,8 +1042,8 @@
       <c r="T7" s="3" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="8" t="n">
-        <v>29.1</v>
+      <c r="U7" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9681.1</v>
+        <v>368</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>21.8</v>
@@ -1086,19 +1086,19 @@
         <v>27.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>22.1</v>
@@ -1110,7 +1110,7 @@
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>10.9</v>
@@ -1125,7 +1125,7 @@
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>94.8</v>
+        <v>4.8</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>23</v>
@@ -1143,7 +1143,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1185</v>
+        <v>1783</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>161.7</v>
@@ -1168,13 +1168,13 @@
         <v>107.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1354.9</v>
+        <v>134.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12100.8</v>
+        <v>100.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>12</v>
@@ -1189,10 +1189,10 @@
         <v>109.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>128.2</v>
+        <v>12.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
@@ -1201,13 +1201,13 @@
         <v>13.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>156.6</v>
+        <v>8556.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>153790.5</v>
+        <v>127.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1216,16 +1216,16 @@
         <v>90.09999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>122</v>
+        <v>32.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1420</v>
+        <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1139.5</v>
+        <v>13.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>589.1</v>
+        <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>29.5</v>
+        <v>256.7</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>21.5</v>
@@ -1259,17 +1259,19 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>17.5</v>
+      <c r="K10" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>21.6</v>
@@ -1293,7 +1295,7 @@
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>161.6</v>
+        <v>61.6</v>
       </c>
       <c r="U10" s="8" t="n">
         <v>18</v>
@@ -1301,14 +1303,14 @@
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1417.8</v>
+        <v>877.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1329,32 +1331,32 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>19.9</v>
+      <c r="D11" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>89.2</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>18.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1378,7 +1380,7 @@
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>156.3</v>
+        <v>256.3</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>22.1</v>
@@ -1396,7 +1398,7 @@
         <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>112.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1417,7 @@
         <v>1218.2</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>82.8</v>
+        <v>32.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>20.2</v>
@@ -1430,10 +1432,10 @@
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>4.8</v>
@@ -1445,7 +1447,7 @@
         <v>20.1</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>97</v>
@@ -1463,7 +1465,7 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>20.8</v>
@@ -1474,14 +1476,14 @@
       <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>13.2</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>111.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1497,7 +1499,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
+        <v>238.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>29.1</v>
@@ -1515,7 +1517,7 @@
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
@@ -1536,7 +1538,7 @@
         <v>97</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>18.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>29.1</v>
@@ -1559,11 +1561,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>800.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6.6</v>
@@ -1582,7 +1584,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>821.4</v>
+        <v>1221.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>27.6</v>
@@ -1606,7 +1608,7 @@
         <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>21.1</v>
@@ -1648,10 +1650,10 @@
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1673,13 +1675,13 @@
         <v>31.4</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>25.9</v>
+        <v>25.3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
@@ -1687,11 +1689,11 @@
       <c r="I15" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J15" s="8" t="n">
-        <v>8</v>
+      <c r="J15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
@@ -1708,7 +1710,7 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1720,10 +1722,10 @@
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
+      <c r="U15" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1733,7 +1735,7 @@
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>716.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>7.4</v>
@@ -1755,37 +1757,37 @@
         <v>15308.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1524.2</v>
+        <v>154.2</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>99.2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>126.8</v>
+        <v>1.8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>524.5</v>
+        <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>162.4</v>
+        <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>102.2</v>
+        <v>2.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1129</v>
+        <v>111.9</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>490</v>
@@ -1797,31 +1799,31 @@
         <v>152.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>125.7</v>
+        <v>25.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.7</v>
+        <v>14.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>412.6</v>
+        <v>12.6</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>251.2</v>
+        <v>212</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>13861.1</v>
+        <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1840,13 +1842,13 @@
         <v>306.2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.9</v>
@@ -1861,7 +1863,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
@@ -1869,16 +1871,16 @@
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>888.6</v>
+      <c r="N17" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
@@ -1888,9 +1890,9 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>1966.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
@@ -1899,11 +1901,11 @@
       <c r="W17" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>141.2</v>
+        <v>772.2</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>18.5</v>
@@ -1925,9 +1927,9 @@
         <v>3341.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E18" s="8" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1936,11 +1938,11 @@
       <c r="G18" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>171.4</v>
+      <c r="H18" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
@@ -1949,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>29.4</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
@@ -1973,7 +1975,7 @@
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20.1</v>
@@ -1984,14 +1986,14 @@
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2021,7 +2023,7 @@
       <c r="G19" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2040,7 +2042,7 @@
         <v>20.7</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
@@ -2048,11 +2050,11 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="8" t="n">
-        <v>55.3</v>
+      <c r="R19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>28.2</v>
@@ -2060,13 +2062,13 @@
       <c r="T19" s="3" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2092,7 +2094,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2899</v>
+        <v>299</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>29.7</v>
@@ -2100,14 +2102,14 @@
       <c r="E20" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2148,10 +2150,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2183,22 +2185,22 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>828.1</v>
-      </c>
-      <c r="H21" s="8" t="n">
+      <c r="G21" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.8</v>
+        <v>3.8</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2213,7 +2215,7 @@
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2239,14 +2241,14 @@
       <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18484.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2262,10 +2264,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>992.9</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>21.2</v>
+        <v>1492.9</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>18</v>
@@ -2273,23 +2275,23 @@
       <c r="F22" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>19.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2298,13 +2300,13 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>10800</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>25.8</v>
@@ -2316,7 +2318,7 @@
         <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24</v>
@@ -2353,16 +2355,16 @@
         <v>155.4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>95.2</v>
+        <v>26.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>125.8</v>
+        <v>225.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2371,7 +2373,7 @@
         <v>18.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>98.40000000000001</v>
@@ -2380,7 +2382,7 @@
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1613.3</v>
+        <v>12.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2392,31 +2394,31 @@
         <v>152.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1240.6</v>
+        <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>115394.7</v>
+        <v>1139.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>796.1</v>
+        <v>795.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.3</v>
+        <v>29.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>12.8</v>
+        <v>118.2</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>140.6</v>
+        <v>141.5</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2432,9 +2434,9 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" s="8" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -2450,16 +2452,16 @@
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2469,7 +2471,7 @@
         <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>30.6</v>
@@ -2515,7 +2517,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>171.8</v>
+        <v>177.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>30.1</v>
@@ -2527,13 +2529,13 @@
         <v>24.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
@@ -2541,11 +2543,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>20</v>
+      <c r="L25" s="8" t="n">
+        <v>110.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>19.8</v>
+        <v>494.4</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2574,7 +2576,7 @@
       <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2600,9 +2602,9 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>845</v>
-      </c>
-      <c r="D26" s="8" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>31.7</v>
       </c>
       <c r="E26" s="3" t="n">
@@ -2615,16 +2617,16 @@
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>886.8</v>
+        <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2633,16 +2635,14 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.1</v>
@@ -2685,9 +2685,9 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1418.2</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
@@ -2696,14 +2696,14 @@
       <c r="F27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>38.7</v>
+      <c r="G27" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
@@ -2717,7 +2717,7 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2744,11 +2744,11 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="8" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>30.2</v>
+      <c r="W27" s="3" t="n">
+        <v>655.1</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2773,7 +2773,7 @@
         <v>282.3</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>32.6</v>
+        <v>25.6</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.8</v>
@@ -2785,7 +2785,7 @@
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>1.9</v>
@@ -2794,7 +2794,7 @@
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
@@ -2811,8 +2811,8 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="8" t="n">
-        <v>979.8</v>
+      <c r="Q28" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2824,7 +2824,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.7</v>
+        <v>12.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2832,11 +2832,11 @@
       <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>659.5</v>
+      <c r="X28" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.2</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>122112.1</v>
+        <v>14</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.2</v>
@@ -2863,8 +2863,8 @@
       <c r="E29" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>47.2</v>
+      <c r="F29" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.9</v>
@@ -2876,14 +2876,14 @@
         <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n">
-        <v>21.9</v>
+      <c r="L29" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>241.9</v>
+        <v>21.5</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>25.4</v>
@@ -2897,7 +2897,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2907,7 +2907,7 @@
         <v>73.7</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>51.5</v>
+        <v>7.3</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>25</v>
@@ -2915,14 +2915,14 @@
       <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.9</v>
+        <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2937,56 +2937,54 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>625.1</v>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>56.5</v>
+        <v>351.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>1120</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>569.8</v>
+        <v>568.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>922.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>114.8</v>
+        <v>11.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>123.7</v>
+        <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>180.2</v>
+        <v>2.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>110.2</v>
+        <v>10.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>122.8</v>
+        <v>111.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>14.5</v>
+        <v>75.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>312.1</v>
+        <v>122</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>183.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3025,19 +3023,17 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>1246.1</v>
+      <c r="D31" s="3" t="n">
+        <v>51.3</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3074,23 +3070,23 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>182.3</v>
+        <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1682.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3120,14 +3116,14 @@
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3169,13 +3165,13 @@
         <v>24.5</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3191,13 +3187,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.8</v>
+        <v>48.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>20.6</v>
+      <c r="E33" s="8" t="n">
+        <v>0.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.9</v>
@@ -3212,10 +3208,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3242,7 +3238,7 @@
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
@@ -3260,7 +3256,7 @@
         <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3277,7 @@
       <c r="D34" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="F34" s="3" t="n">
@@ -3296,7 +3292,9 @@
       <c r="I34" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
@@ -3313,7 +3311,7 @@
         <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>30.1</v>
@@ -3325,25 +3323,25 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>20.6</v>
+        <v>70.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>182.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3385,14 +3383,14 @@
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>18.9</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3410,7 +3408,7 @@
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3422,13 +3420,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>2959.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>164.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3444,7 +3442,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
+        <v>117.2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.6</v>
@@ -3456,7 +3454,7 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>19</v>
@@ -3465,7 +3463,7 @@
         <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.3</v>
@@ -3483,7 +3481,7 @@
         <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3497,14 +3495,12 @@
       <c r="T36" s="3" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>20.8</v>
+        <v>61.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
@@ -3513,7 +3509,7 @@
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3535,10 +3531,10 @@
         <v>142.9</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1121.5</v>
+        <v>182.1</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>42.9</v>
@@ -3550,55 +3546,55 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.9</v>
+        <v>1807.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>28.8</v>
+        <v>22.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>92</v>
+        <v>20.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.8</v>
+        <v>32.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>233.1</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>127.2</v>
+        <v>117.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>136.3</v>
+        <v>13.6</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>393.6</v>
+        <v>3923.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>124.1</v>
+        <v>24.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>11.2</v>
+        <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>129.8</v>
+        <v>12.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>12466</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3614,7 +3610,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>155.3</v>
+        <v>165.3</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>28.6</v>
@@ -3634,17 +3630,17 @@
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>11.8</v>
+      <c r="J38" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3655,32 +3651,32 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.6</v>
+      <c r="Q38" s="8" t="n">
+        <v>56.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>27.3</v>
+        <v>48.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>828.7</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>28.8</v>
+        <v>24.8</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3699,7 +3695,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332</v>
+        <v>33.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>30.7</v>
@@ -3713,14 +3709,14 @@
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3738,7 +3734,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>30.7</v>
@@ -3750,7 +3746,7 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6685.3</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
@@ -3761,8 +3757,8 @@
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>17.8</v>
+      <c r="X39" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
@@ -3784,9 +3780,9 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="D40" s="8" t="n">
+        <v>2728.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E40" s="3" t="n">
@@ -3798,14 +3794,14 @@
       <c r="G40" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>29</v>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3816,8 +3812,8 @@
       <c r="M40" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>24.6</v>
+      <c r="N40" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
@@ -3826,10 +3822,10 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>80.7</v>
+        <v>30.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
@@ -3838,7 +3834,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28</v>
@@ -3853,7 +3849,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1811.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3869,7 +3865,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>248.6</v>
+        <v>242.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>29.6</v>
@@ -3893,7 +3889,7 @@
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>20.9</v>
@@ -3910,17 +3906,17 @@
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="R41" s="8" t="n">
+      <c r="Q41" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>80.5</v>
+        <v>20.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
@@ -3935,9 +3931,11 @@
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3966,14 +3964,14 @@
       <c r="G42" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -3981,8 +3979,8 @@
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="3" t="n">
-        <v>21.2</v>
+      <c r="M42" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
@@ -3991,7 +3989,7 @@
         <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>18</v>
+        <v>80.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>30.9</v>
@@ -4014,11 +4012,11 @@
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>8953.5</v>
+      <c r="X42" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>16.5</v>
@@ -4037,25 +4035,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="3" t="n">
         <v>21</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>25.9</v>
+        <v>45.1</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>41.6</v>
+      <c r="I43" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4076,7 +4074,7 @@
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4100,10 +4098,10 @@
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1849.5</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>0.6</v>
@@ -4164,47 +4162,47 @@
         <v>1423.4</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>922.7</v>
+        <v>22.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>70.5</v>
+        <v>102.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>10101.1</v>
+        <v>124.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>12101</v>
+        <v>190.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>82.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>164.9</v>
+        <v>1814.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>100900160.4</v>
+        <v>105081.6</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>16128.5</v>
+        <v>1820.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>4916</v>
+        <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
+        <v>16.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1246.3</v>
+        <v>846.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>122.2</v>
+        <v>63.3</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>13.8</v>
@@ -4216,19 +4214,19 @@
         <v>66.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>222</v>
+        <v>34</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>1412.4</v>
+        <v>112.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>122.5</v>
+        <v>12.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>3983.1</v>
+        <v>9929.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>10820.9</v>
+        <v>80.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4246,7 +4244,7 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="E46" s="3" t="n">
@@ -4255,11 +4253,11 @@
       <c r="F46" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4268,13 +4266,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
@@ -4285,35 +4283,35 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>29.9</v>
+      <c r="Q46" s="8" t="n">
+        <v>95.3</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S46" s="8" t="n">
-        <v>71.7</v>
+      <c r="S46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V46" s="8" t="n">
+      <c r="U46" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V46" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>73.8</v>
+      <c r="W46" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>128.5</v>
+        <v>28.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,7 +739,7 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>22.7</v>
@@ -757,7 +757,7 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -769,21 +769,21 @@
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.4</v>
+        <v>27.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -798,13 +798,15 @@
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>92.09999999999999</v>
+      <c r="X4" s="3" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -848,8 +850,8 @@
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>22.4</v>
+      <c r="M5" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -870,10 +872,10 @@
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.4</v>
+        <v>27.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -885,10 +887,10 @@
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -904,7 +906,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -916,7 +918,7 @@
         <v>26.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>20.3</v>
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -925,7 +927,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -940,10 +942,10 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>972</v>
+        <v>97</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>31.4</v>
@@ -955,7 +957,7 @@
         <v>27.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>18.6</v>
@@ -973,7 +975,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -989,7 +991,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8218.200000000001</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>32.4</v>
@@ -1004,16 +1006,16 @@
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1</v>
+        <v>10.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1021,7 +1023,7 @@
       <c r="M7" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1030,7 +1032,7 @@
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
@@ -1051,7 +1053,7 @@
       <c r="W7" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
@@ -1074,13 +1076,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>21.8</v>
+      <c r="E8" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>27.5</v>
@@ -1092,7 +1094,7 @@
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
@@ -1110,10 +1112,10 @@
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98.5</v>
+        <v>196.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>33.3</v>
@@ -1121,13 +1123,13 @@
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U8" s="8" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1136,14 +1138,14 @@
       <c r="W8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783</v>
+        <v>1783.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>161.7</v>
@@ -1171,7 +1173,7 @@
         <v>134.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5.4</v>
+        <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>100.8</v>
@@ -1192,22 +1194,22 @@
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>12.8</v>
+        <v>128.2</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>8556.6</v>
+        <v>255.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.5</v>
+        <v>137.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1216,19 +1218,19 @@
         <v>90.09999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>32.7</v>
+        <v>135.7</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>13.9</v>
+        <v>139.5</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+        <v>141.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1244,13 +1246,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>256.7</v>
+        <v>356.7</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>21.5</v>
+        <v>32.3</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.9</v>
@@ -1259,19 +1261,19 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>21.6</v>
@@ -1283,7 +1285,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>31.1</v>
@@ -1297,7 +1299,7 @@
       <c r="T10" s="3" t="n">
         <v>61.6</v>
       </c>
-      <c r="U10" s="8" t="n">
+      <c r="U10" s="3" t="n">
         <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
@@ -1310,10 +1312,10 @@
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>877.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1334,26 +1336,26 @@
       <c r="D11" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>18.1</v>
+        <v>14.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.6</v>
@@ -1380,7 +1382,7 @@
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>256.3</v>
+        <v>56.3</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>22.1</v>
@@ -1395,10 +1397,10 @@
         <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>112.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1416,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1218.2</v>
+        <v>2418.2</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>32.8</v>
@@ -1428,14 +1430,14 @@
       <c r="G12" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>4.8</v>
@@ -1446,7 +1448,7 @@
       <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1467,7 +1469,7 @@
       <c r="T12" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="V12" s="3" t="n">
@@ -1476,11 +1478,11 @@
       <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="8" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>713.2</v>
+        <v>173.2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>11.1</v>
@@ -1499,7 +1501,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>238.1</v>
+        <v>230.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>29.1</v>
@@ -1517,7 +1519,7 @@
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
@@ -1531,14 +1533,14 @@
       <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>29.1</v>
@@ -1568,7 +1570,7 @@
         <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1584,12 +1586,12 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1221.4</v>
+        <v>121.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="F14" s="3" t="n">
@@ -1599,7 +1601,7 @@
         <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>87.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
@@ -1616,7 +1618,7 @@
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
@@ -1650,10 +1652,10 @@
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>185.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1669,7 +1671,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>340.8</v>
+        <v>2340.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>31.4</v>
@@ -1690,7 +1692,7 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1701,7 +1703,7 @@
       <c r="M15" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1710,7 +1712,7 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1725,11 +1727,11 @@
       <c r="U15" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>21.9</v>
+      <c r="W15" s="8" t="n">
+        <v>41.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.3</v>
@@ -1754,22 +1756,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15308.1</v>
+        <v>1530.8</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>154.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.8</v>
+        <v>226.8</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1781,13 +1783,13 @@
         <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.9</v>
+        <v>102.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>10.1</v>
+        <v>101.9</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>111.9</v>
+        <v>119</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>490</v>
@@ -1799,22 +1801,22 @@
         <v>152.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>25.7</v>
+        <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>14.2</v>
+        <v>142.7</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>7.6</v>
+        <v>76.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>12.6</v>
+        <v>136.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>212</v>
+        <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
@@ -1823,7 +1825,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>142.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1839,16 +1841,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
+        <v>230.6</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.9</v>
@@ -1863,7 +1865,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
@@ -1890,7 +1892,7 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>1966.2</v>
+        <v>166.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
@@ -1905,10 +1907,10 @@
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>772.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1924,28 +1926,28 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3341.1</v>
+        <v>33.2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1953,17 +1955,17 @@
       <c r="L18" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>32.2</v>
@@ -1977,7 +1979,7 @@
       <c r="T18" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="V18" s="3" t="n">
@@ -1993,7 +1995,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2009,9 +2011,9 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.2</v>
       </c>
       <c r="E19" s="3" t="n">
@@ -2041,7 +2043,7 @@
       <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
@@ -2071,7 +2073,7 @@
       <c r="W19" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="3" t="n">
+      <c r="X19" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2096,7 +2098,7 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="8" t="n">
         <v>29.7</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -2105,11 +2107,11 @@
       <c r="F20" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="8" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2120,13 +2122,13 @@
       <c r="K20" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="8" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="N20" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2179,13 +2181,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
+        <v>35.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>28</v>
+      <c r="E21" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>24.1</v>
@@ -2193,7 +2195,7 @@
       <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2209,13 +2211,13 @@
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="N21" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2245,7 +2247,7 @@
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>1844.1</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>5.4</v>
@@ -2264,22 +2266,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1492.9</v>
+        <v>294.9</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.2</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>25</v>
+        <v>18.8</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>238</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17.4</v>
+        <v>167.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
@@ -2291,12 +2293,12 @@
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2306,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>25.8</v>
@@ -2315,22 +2317,22 @@
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>66.8</v>
+        <v>166.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.3</v>
@@ -2349,22 +2351,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
+        <v>161</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>155.4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>26.2</v>
+        <v>96.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>225.8</v>
+        <v>125.8</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.8</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2382,7 +2384,7 @@
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12.2</v>
+        <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2397,28 +2399,28 @@
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1139.7</v>
+        <v>139.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>795.1</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>29.2</v>
+        <v>129.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>118.2</v>
+        <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>141.5</v>
+        <v>140.6</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>126.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2434,12 +2436,12 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>380.3</v>
+        <v>322</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="F24" s="3" t="n">
@@ -2454,21 +2456,23 @@
       <c r="I24" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K24" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4</v>
+        <v>98.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.3</v>
@@ -2483,13 +2487,13 @@
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>25.9</v>
+        <v>2.5</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>23.8</v>
@@ -2535,7 +2539,7 @@
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.4</v>
+        <v>11.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
@@ -2543,11 +2547,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="8" t="n">
-        <v>110.4</v>
+      <c r="L25" s="3" t="n">
+        <v>40.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>494.4</v>
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2576,7 +2580,7 @@
       <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2623,7 +2627,7 @@
         <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0</v>
@@ -2635,20 +2639,22 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>15.8</v>
+        <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q26" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>55.2</v>
@@ -2697,13 +2703,13 @@
         <v>28.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.7</v>
+        <v>13.7</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>13.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
@@ -2717,7 +2723,7 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2745,10 +2751,10 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>655.1</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2770,21 +2776,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.3</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>25.6</v>
+        <v>32.6</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>26.8</v>
+      <c r="F28" s="8" t="n">
+        <v>68.2</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2796,7 +2802,7 @@
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2829,17 +2835,17 @@
       <c r="V28" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
+      <c r="X28" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.2</v>
+        <v>14.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2861,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14</v>
+        <v>146.2</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.2</v>
@@ -2878,9 +2884,11 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="8" t="n">
-        <v>18.9</v>
+      <c r="K29" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>21.5</v>
@@ -2897,7 +2905,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2906,8 +2914,8 @@
       <c r="T29" s="3" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="8" t="n">
-        <v>7.3</v>
+      <c r="U29" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>25</v>
@@ -2922,7 +2930,7 @@
         <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2937,39 +2945,41 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>136.3</v>
+      </c>
       <c r="D30" s="3" t="n">
-        <v>351.5</v>
+        <v>1156.5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1120</v>
+        <v>128</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>568.1</v>
+        <v>256.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>922.8</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.7</v>
+        <v>1171.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>2.2</v>
+        <v>102.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.1</v>
+        <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>111.3</v>
+        <v>117.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
@@ -2978,13 +2988,13 @@
         <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>75.5</v>
+        <v>145.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>183.5</v>
+        <v>13.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -2999,10 +3009,10 @@
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>13.3</v>
+        <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>411.5</v>
+        <v>2411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3023,8 +3033,8 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>51.3</v>
+      <c r="D31" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.9</v>
@@ -3032,7 +3042,9 @@
       <c r="F31" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
@@ -3040,9 +3052,11 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+        <v>13.4</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>20.4</v>
       </c>
@@ -3053,7 +3067,7 @@
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
@@ -3071,12 +3085,12 @@
         <v>68.90000000000001</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>13.8</v>
+        <v>113.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3086,7 +3100,7 @@
         <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3104,11 +3118,11 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="8" t="n">
         <v>29</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20.4</v>
+        <v>40.4</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>24.7</v>
@@ -3116,14 +3130,14 @@
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3131,7 +3145,7 @@
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3149,7 +3163,7 @@
       <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
@@ -3162,16 +3176,16 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X32" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X32" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>181.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3187,13 +3201,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>48.1</v>
+        <v>44.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="8" t="n">
-        <v>0.6</v>
+      <c r="E33" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.9</v>
@@ -3205,13 +3219,13 @@
         <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>22.5</v>
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3219,7 +3233,7 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
@@ -3238,7 +3252,7 @@
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
@@ -3255,9 +3269,7 @@
       <c r="Y33" s="3" t="n">
         <v>91.8</v>
       </c>
-      <c r="Z33" s="3" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3293,18 +3305,18 @@
         <v>11.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
@@ -3390,13 +3402,13 @@
         <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
@@ -3420,10 +3432,10 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>95.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>85.8</v>
+        <v>185.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>14.9</v>
@@ -3442,9 +3454,9 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="D36" s="3" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3454,10 +3466,10 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3466,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3474,7 +3486,7 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
@@ -3495,21 +3507,23 @@
       <c r="T36" s="3" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>61.8</v>
+        <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3531,13 +3545,13 @@
         <v>142.9</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>182.1</v>
+        <v>121.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>42.9</v>
+        <v>142.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3546,49 +3560,49 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1807.9</v>
+        <v>17.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>22.9</v>
+        <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>20.2</v>
+        <v>120.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>32.2</v>
+        <v>495</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.8</v>
+        <v>133.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117.2</v>
+        <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>13.6</v>
+        <v>136.3</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3923.6</v>
+        <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>24.1</v>
+        <v>124.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>112.2</v>
+        <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>12.2</v>
+        <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>416</v>
@@ -3610,7 +3624,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
+        <v>16.5</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>28.6</v>
@@ -3619,28 +3633,28 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>24.3</v>
+        <v>2.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3651,23 +3665,23 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
-        <v>56.6</v>
+      <c r="Q38" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>48.5</v>
+        <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>24.8</v>
+        <v>84.8</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>22.5</v>
@@ -3676,10 +3690,10 @@
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3695,7 +3709,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>33.2</v>
+        <v>332.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>30.7</v>
@@ -3706,20 +3720,20 @@
       <c r="F39" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K39" s="3" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.5</v>
@@ -3734,7 +3748,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>30.7</v>
@@ -3746,10 +3760,10 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>27.8</v>
@@ -3757,14 +3771,14 @@
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>172.9</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3780,13 +3794,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2728.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>20.6</v>
+      <c r="E40" s="8" t="n">
+        <v>200.6</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>25.7</v>
@@ -3810,10 +3824,10 @@
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>42.6</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
@@ -3831,7 +3845,7 @@
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>165.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
@@ -3839,7 +3853,7 @@
       <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3849,7 +3863,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>120.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3867,7 +3881,7 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="8" t="n">
         <v>29.6</v>
       </c>
       <c r="E41" s="3" t="n">
@@ -3883,11 +3897,9 @@
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -3895,7 +3907,7 @@
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>26.2</v>
+        <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
@@ -3916,25 +3928,25 @@
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
+        <v>720.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X41" s="3" t="n">
+      <c r="X41" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>841.1</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3979,17 +3991,17 @@
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
+      <c r="M42" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>30.9</v>
@@ -4009,11 +4021,11 @@
       <c r="V42" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>81.8</v>
@@ -4044,16 +4056,16 @@
         <v>21</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>45.1</v>
+        <v>25.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>18.6</v>
+        <v>19.7</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4067,14 +4079,14 @@
       <c r="M43" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4082,14 +4094,14 @@
       <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="3" t="n">
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>77</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>24</v>
@@ -4097,14 +4109,14 @@
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>85.40000000000001</v>
+      <c r="X43" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4162,13 +4174,13 @@
         <v>1423.4</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>22.7</v>
+        <v>52.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>102.7</v>
+        <v>802.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>124.5</v>
+        <v>1127.8</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>190.6</v>
@@ -4177,56 +4189,58 @@
         <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1814.9</v>
+        <v>114.9</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>105081.6</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr"/>
+        <v>103.8</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>102.9</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>1820.5</v>
+        <v>120.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>846.3</v>
+        <v>146.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>63.3</v>
+        <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>13.8</v>
+        <v>138.4</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>66.8</v>
+        <v>166</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>34</v>
+        <v>1234</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>112.8</v>
+        <v>219</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>12.2</v>
+        <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>9929.5</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>80.5</v>
+        <v>38</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4253,11 +4267,11 @@
       <c r="F46" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>9.1</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4266,13 +4280,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
@@ -4283,11 +4297,11 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>95.3</v>
+      <c r="Q46" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>24.5</v>
+        <v>2.4</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>27.8</v>
@@ -4304,14 +4318,14 @@
       <c r="W46" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>7.7</v>
+        <v>78.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -851,7 +842,7 @@
         <v>21.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -875,7 +866,7 @@
         <v>78</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>27.4</v>
+        <v>7.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -887,7 +878,7 @@
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>10</v>
@@ -906,7 +897,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2368</v>
+        <v>368</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>31.4</v>
@@ -991,7 +982,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
+        <v>18.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>32.4</v>
@@ -1015,7 +1006,7 @@
         <v>4.1</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1023,7 +1014,7 @@
       <c r="M7" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1076,13 +1067,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368</v>
+        <v>368</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>41.8</v>
+      <c r="E8" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>27.5</v>
@@ -1112,7 +1103,7 @@
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.9</v>
@@ -1123,13 +1114,13 @@
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>54.8</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1145,7 +1136,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
         <v>3.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>255.6</v>
+        <v>155.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
@@ -1230,7 +1221,7 @@
         <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.8</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1251,8 +1242,8 @@
       <c r="D10" s="3" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>13.5</v>
+      <c r="E10" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.9</v>
@@ -1261,7 +1252,7 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1285,7 +1276,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>31.1</v>
@@ -1337,19 +1328,19 @@
         <v>33.3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+      <c r="H11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0</v>
@@ -1416,7 +1407,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2418.2</v>
+        <v>18.2</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>32.8</v>
@@ -1430,11 +1421,11 @@
       <c r="G12" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5</v>
@@ -1448,7 +1439,7 @@
       <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1469,7 +1460,7 @@
       <c r="T12" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="8" t="n">
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="V12" s="3" t="n">
@@ -1478,11 +1469,11 @@
       <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>173.2</v>
+        <v>73.2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>11.1</v>
@@ -1519,7 +1510,7 @@
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
@@ -1533,7 +1524,7 @@
       <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1570,7 +1561,7 @@
         <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1591,7 +1582,7 @@
       <c r="D14" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="F14" s="3" t="n">
@@ -1600,14 +1591,14 @@
       <c r="G14" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1618,7 +1609,7 @@
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
@@ -1652,10 +1643,10 @@
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1671,7 +1662,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2340.8</v>
+        <v>340.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>31.4</v>
@@ -1692,7 +1683,7 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1703,7 +1694,7 @@
       <c r="M15" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1730,8 +1721,8 @@
       <c r="V15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>41.9</v>
+      <c r="W15" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.3</v>
@@ -1765,13 +1756,13 @@
         <v>99.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>226.8</v>
+        <v>126.8</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1825,7 +1816,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>142.3</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1832,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>230.6</v>
+        <v>306.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30.8</v>
@@ -1850,7 +1841,7 @@
         <v>19.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.9</v>
@@ -1865,7 +1856,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
@@ -1892,7 +1883,7 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
@@ -1926,7 +1917,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33.2</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.2</v>
@@ -1934,10 +1925,10 @@
       <c r="E18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -1952,20 +1943,20 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>32.2</v>
@@ -1979,7 +1970,7 @@
       <c r="T18" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="8" t="n">
+      <c r="U18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="V18" s="3" t="n">
@@ -1995,7 +1986,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2011,9 +2002,9 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>32.2</v>
       </c>
       <c r="E19" s="3" t="n">
@@ -2043,7 +2034,7 @@
       <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
@@ -2073,7 +2064,7 @@
       <c r="W19" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2098,7 +2089,7 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="3" t="n">
         <v>29.7</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -2107,14 +2098,14 @@
       <c r="F20" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>118.4</v>
+      <c r="H20" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.5</v>
@@ -2125,10 +2116,10 @@
       <c r="L20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="N20" s="8" t="n">
+      <c r="M20" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2181,12 +2172,12 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>35.7</v>
+        <v>357.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
@@ -2195,7 +2186,7 @@
       <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2207,17 +2198,17 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2247,7 +2238,7 @@
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>1844.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>5.4</v>
@@ -2271,20 +2262,20 @@
       <c r="D22" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>238</v>
+      <c r="F22" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>167.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
@@ -2292,13 +2283,13 @@
       <c r="K22" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2317,7 +2308,7 @@
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2325,14 +2316,14 @@
       <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.3</v>
@@ -2387,7 +2378,7 @@
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>94</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
@@ -2420,7 +2411,7 @@
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2460,12 +2451,12 @@
         <v>3.7</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2487,13 +2478,13 @@
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>2.5</v>
+        <v>25.9</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>23.8</v>
@@ -2505,7 +2496,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+        <v>25.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2530,7 @@
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
@@ -2606,7 +2597,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
+        <v>345</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>31.7</v>
@@ -2620,7 +2611,7 @@
       <c r="G26" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2691,7 +2682,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
+        <v>18.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>32.9</v>
@@ -2700,16 +2691,16 @@
         <v>19.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
@@ -2754,7 +2745,7 @@
         <v>25.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2776,16 +2767,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="D28" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>68.2</v>
+      <c r="F28" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>12.8</v>
@@ -2802,11 +2793,11 @@
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>29.9</v>
+        <v>19.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
@@ -2835,17 +2826,17 @@
       <c r="V28" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2896,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2930,7 +2921,7 @@
         <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2946,10 +2937,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>136.3</v>
+        <v>1363.5</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1156.5</v>
+        <v>156.5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>99.59999999999999</v>
@@ -2958,16 +2949,16 @@
         <v>128</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>256.9</v>
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1171.8</v>
+        <v>17.1</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>23.7</v>
@@ -2994,7 +2985,7 @@
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>135.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3012,7 +3003,7 @@
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>2411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3033,7 +3024,7 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="3" t="n">
         <v>31.3</v>
       </c>
       <c r="E31" s="3" t="n">
@@ -3052,7 +3043,7 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
@@ -3067,7 +3058,7 @@
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
@@ -3084,16 +3075,16 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>113.8</v>
+      <c r="U31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
@@ -3118,7 +3109,7 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E32" s="3" t="n">
@@ -3130,14 +3121,14 @@
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3145,7 +3136,7 @@
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3163,7 +3154,7 @@
       <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
@@ -3176,16 +3167,16 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X32" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3225,7 +3216,7 @@
         <v>0.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3233,7 +3224,7 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
@@ -3252,7 +3243,7 @@
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
@@ -3298,11 +3289,11 @@
       <c r="G34" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.3</v>
@@ -3310,13 +3301,13 @@
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
@@ -3343,7 +3334,7 @@
       <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3374,7 +3365,7 @@
       <c r="D35" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="F35" s="3" t="n">
@@ -3383,7 +3374,7 @@
       <c r="G35" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3401,8 +3392,8 @@
       <c r="M35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>13.9</v>
+      <c r="N35" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3420,7 +3411,7 @@
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>25.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3431,14 +3422,14 @@
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="X35" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>185.8</v>
+        <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3454,9 +3445,9 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="8" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3466,10 +3457,10 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>119</v>
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3486,7 +3477,7 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
@@ -3520,7 +3511,7 @@
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3551,7 +3542,7 @@
         <v>121.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>142.9</v>
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3578,7 +3569,7 @@
         <v>495</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>133.1</v>
@@ -3605,7 +3596,7 @@
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>16</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3624,7 +3615,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.5</v>
+        <v>165.3</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>28.6</v>
@@ -3633,12 +3624,12 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2.4</v>
+        <v>24.3</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
@@ -3648,7 +3639,7 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3675,13 +3666,13 @@
         <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>22.5</v>
@@ -3690,10 +3681,10 @@
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3700,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.3</v>
+        <v>332.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>30.7</v>
@@ -3720,17 +3711,17 @@
       <c r="F39" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -3739,7 +3730,7 @@
         <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>22.6</v>
@@ -3760,10 +3751,10 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>27.8</v>
@@ -3771,11 +3762,11 @@
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>172.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>0</v>
@@ -3796,11 +3787,11 @@
       <c r="C40" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>200.6</v>
+      <c r="E40" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>25.7</v>
@@ -3812,7 +3803,7 @@
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.1</v>
@@ -3824,9 +3815,9 @@
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
@@ -3845,7 +3836,7 @@
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
@@ -3853,7 +3844,7 @@
       <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3863,7 +3854,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>120.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3881,7 +3872,7 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="E41" s="3" t="n">
@@ -3897,11 +3888,11 @@
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>20.9</v>
@@ -3928,22 +3919,22 @@
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
+        <v>70.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="8" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>841.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>6.7</v>
@@ -3980,7 +3971,7 @@
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
@@ -3994,7 +3985,7 @@
       <c r="M42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4021,7 +4012,7 @@
       <c r="V42" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4031,7 +4022,7 @@
         <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4059,13 +4050,13 @@
         <v>25.9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4079,14 +4070,14 @@
       <c r="M43" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4094,7 +4085,7 @@
       <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4109,7 +4100,7 @@
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="8" t="n">
+      <c r="X43" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y43" s="3" t="n">
@@ -4171,19 +4162,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1423.4</v>
+        <v>1453.4</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>52.7</v>
+        <v>152.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>802.1</v>
+        <v>102.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1127.8</v>
+        <v>127.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>190.6</v>
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
@@ -4192,7 +4183,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>114.9</v>
+        <v>14.9</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>5</v>
@@ -4210,7 +4201,7 @@
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>146.3</v>
@@ -4225,19 +4216,19 @@
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1234</v>
+        <v>234</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>392.3</v>
+        <v>92.3</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>38</v>
@@ -4270,17 +4261,17 @@
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
@@ -4301,10 +4292,10 @@
         <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>2.4</v>
+        <v>24.5</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
@@ -4318,14 +4309,14 @@
       <c r="W46" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.5</v>
+        <v>78.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>78.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>32.4</v>
@@ -1194,7 +1194,7 @@
         <v>3.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>155.6</v>
+        <v>156.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
@@ -1252,7 +1252,7 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1261,7 +1261,7 @@
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>21.9</v>
@@ -1291,7 +1291,7 @@
         <v>61.6</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>33.3</v>
@@ -1343,7 +1343,7 @@
         <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>32.8</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.2</v>
@@ -2178,7 +2178,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>24.1</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2378,7 +2378,7 @@
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>32.9</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>28.2</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>32.6</v>
@@ -3003,7 +3003,7 @@
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3046,7 +3046,7 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>20.4</v>
@@ -3393,7 +3393,7 @@
         <v>19</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3596,7 +3596,7 @@
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3684,7 +3684,7 @@
         <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -3730,7 +3730,7 @@
         <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>22.6</v>
@@ -3815,7 +3815,7 @@
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>24.6</v>
@@ -4219,7 +4219,7 @@
         <v>66</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>119</v>
@@ -4228,10 +4228,10 @@
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>92.3</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_decimal_place_correction.xlsx
@@ -1194,7 +1194,7 @@
         <v>3.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>156.6</v>
+        <v>155.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
@@ -1291,7 +1291,7 @@
         <v>61.6</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
@@ -1322,13 +1322,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>26.6</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.2</v>
@@ -2178,7 +2178,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>24.1</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2581,7 +2581,7 @@
         <v>95.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
+        <v>28.2</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>32.6</v>
@@ -3393,7 +3393,7 @@
         <v>19</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3511,7 +3511,7 @@
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>94.8</v>
+        <v>924.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3639,7 +3639,7 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3684,7 +3684,7 @@
         <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -4056,7 +4056,7 @@
         <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
+        <v>145.3</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>152.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>102.1</v>
+        <v>103.1</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>127.4</v>
@@ -4225,13 +4225,13 @@
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>138.1</v>
+        <v>13.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
